--- a/tools/predictor_table.xlsx
+++ b/tools/predictor_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LULCC_CH_Ensemble\Tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LULCC_CH_HPC\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F7BDFC-82DE-4F85-8F34-3AFA0A191CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8B7F7F-D102-4DD2-93C6-86F41764E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4173,72 +4173,18 @@
     <t>https://zenodo.org/record/7590103#.Y-KKIpDYqUk</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP26_2020.tif</t>
-  </si>
-  <si>
-    <t>RCP26</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP45_2020.tif</t>
-  </si>
-  <si>
-    <t>RCP45</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP85_2020.tif</t>
-  </si>
-  <si>
-    <t>RCP85</t>
-  </si>
-  <si>
     <t>Average_Sum_gdays_0deg</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2016_2020_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2016_2020_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2016_2020_average_RCP85.tif</t>
-  </si>
-  <si>
     <t>Average_Sum_gdays_3deg</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2016_2020_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2016_2020_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2016_2020_average_RCP85.tif</t>
-  </si>
-  <si>
     <t>Average_Sum_gdays_5deg</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2016_2020_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2016_2020_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2016_2020_average_RCP85.tif</t>
-  </si>
-  <si>
     <t>Average_Avg_precip</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP26_2020.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP45_2020.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP85_2020.tif</t>
-  </si>
-  <si>
     <t>2025_2030</t>
   </si>
   <si>
@@ -4287,51 +4233,6 @@
     <t>Data/Preds/Prepared/Layers/Socio_economic/Employment/Avg_chg_FTE_Sec3_2025_2030_Ref_Peri_urban.tif</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP26_2025.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP45_2025.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP85_2025.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2021_2025_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2021_2025_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2021_2025_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2021_2025_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2021_2025_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2021_2025_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2021_2025_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2021_2025_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2021_2025_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP26_2025.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP45_2025.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP85_2025.tif</t>
-  </si>
-  <si>
     <t>2030_2035</t>
   </si>
   <si>
@@ -4380,51 +4281,6 @@
     <t>Data/Preds/Prepared/Layers/Socio_economic/Employment/Avg_chg_FTE_Sec3_2030_2035_Ref_Peri_urban.tif</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP26_2030.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP45_2030.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP85_2030.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2026_2030_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2026_2030_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2026_2030_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2026_2030_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2026_2030_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2026_2030_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2026_2030_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2026_2030_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2026_2030_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP26_2030.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP45_2030.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP85_2030.tif</t>
-  </si>
-  <si>
     <t>2035_2040</t>
   </si>
   <si>
@@ -4473,51 +4329,6 @@
     <t>Data/Preds/Prepared/Layers/Socio_economic/Employment/Avg_chg_FTE_Sec3_2035_2040_Ref_Peri_urban.tif</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP26_2035.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP45_2035.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP85_2035.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2031_2035_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2031_2035_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2031_2035_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2031_2035_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2031_2035_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2031_2035_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2031_2035_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2031_2035_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2031_2035_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP26_2035.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP45_2035.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP85_2035.tif</t>
-  </si>
-  <si>
     <t>2040_2045</t>
   </si>
   <si>
@@ -4566,51 +4377,6 @@
     <t>Data/Preds/Prepared/Layers/Socio_economic/Employment/Avg_chg_FTE_Sec3_2040_2045_Ref_Peri_urban.tif</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP26_2040.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP45_2040.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP85_2040.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2036_2040_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2036_2040_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2036_2040_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2036_2040_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2036_2040_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2036_2040_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2036_2040_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2036_2040_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2036_2040_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP26_2040.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP45_2040.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP85_2040.tif</t>
-  </si>
-  <si>
     <t>2045_2050</t>
   </si>
   <si>
@@ -4659,51 +4425,6 @@
     <t>Data/Preds/Prepared/Layers/Socio_economic/Employment/Avg_chg_FTE_Sec3_2045_2050_Ref_Peri_urban.tif</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP26_2045.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP45_2045.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP85_2045.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2041_2045_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2041_2045_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2041_2045_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2041_2045_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2041_2045_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2041_2045_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2041_2045_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2041_2045_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2041_2045_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP26_2045.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP45_2045.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP85_2045.tif</t>
-  </si>
-  <si>
     <t>2050_2055</t>
   </si>
   <si>
@@ -4752,51 +4473,6 @@
     <t>Data/Preds/Prepared/Layers/Socio_economic/Employment/Avg_chg_FTE_Sec3_2050_2055_Ref_Peri_urban.tif</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP26_2050.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP45_2050.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP85_2050.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2046_2050_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2046_2050_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2046_2050_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2046_2050_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2046_2050_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2046_2050_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2046_2050_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2046_2050_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2046_2050_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP26_2050.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP45_2050.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP85_2050.tif</t>
-  </si>
-  <si>
     <t>2055_2060</t>
   </si>
   <si>
@@ -4845,97 +4521,421 @@
     <t>Data/Preds/Prepared/Layers/Socio_economic/Employment/Avg_chg_FTE_Sec3_2055_2060_Ref_Peri_urban.tif</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP26_2055.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP45_2055.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP85_2055.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2051_2055_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2051_2055_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2051_2055_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2051_2055_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2051_2055_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2051_2055_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2051_2055_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2051_2055_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2051_2055_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP26_2055.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP45_2055.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP85_2055.tif</t>
-  </si>
-  <si>
     <t>2060_2065</t>
   </si>
   <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP26_2060.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP45_2060.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_RCP85_2060.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2056_2060_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2056_2060_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2056_2060_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2056_2060_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2056_2060_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2056_2060_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2056_2060_average_RCP26.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2056_2060_average_RCP45.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2056_2060_average_RCP85.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP26_2060.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP45_2060.tif</t>
-  </si>
-  <si>
-    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_RCP85_2060.tif</t>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp26_2020.tif</t>
+  </si>
+  <si>
+    <t>rcp26</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp45_2020.tif</t>
+  </si>
+  <si>
+    <t>rcp45</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp85_2020.tif</t>
+  </si>
+  <si>
+    <t>rcp85</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2016_2020_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2016_2020_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2016_2020_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2016_2020_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2016_2020_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2016_2020_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2016_2020_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2016_2020_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2016_2020_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp26_2020.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp45_2020.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp85_2020.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp26_2025.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp45_2025.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp85_2025.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2021_2025_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2021_2025_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2021_2025_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2021_2025_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2021_2025_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2021_2025_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2021_2025_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2021_2025_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2021_2025_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp26_2025.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp45_2025.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp85_2025.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp26_2030.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp45_2030.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp85_2030.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2026_2030_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2026_2030_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2026_2030_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2026_2030_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2026_2030_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2026_2030_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2026_2030_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2026_2030_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2026_2030_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp26_2030.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp45_2030.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp85_2030.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp26_2035.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp45_2035.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp85_2035.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2031_2035_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2031_2035_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2031_2035_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2031_2035_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2031_2035_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2031_2035_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2031_2035_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2031_2035_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2031_2035_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp26_2035.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp45_2035.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp85_2035.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp26_2040.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp45_2040.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp85_2040.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2036_2040_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2036_2040_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2036_2040_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2036_2040_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2036_2040_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2036_2040_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2036_2040_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2036_2040_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2036_2040_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp26_2040.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp45_2040.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp85_2040.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp26_2045.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp45_2045.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp85_2045.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2041_2045_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2041_2045_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2041_2045_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2041_2045_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2041_2045_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2041_2045_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2041_2045_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2041_2045_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2041_2045_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp26_2045.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp45_2045.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp85_2045.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp26_2050.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp45_2050.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp85_2050.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2046_2050_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2046_2050_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2046_2050_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2046_2050_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2046_2050_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2046_2050_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2046_2050_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2046_2050_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2046_2050_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp26_2050.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp45_2050.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp85_2050.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp26_2055.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp45_2055.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp85_2055.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2051_2055_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2051_2055_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2051_2055_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2051_2055_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2051_2055_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2051_2055_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2051_2055_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2051_2055_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2051_2055_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp26_2055.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp45_2055.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp85_2055.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp26_2060.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp45_2060.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_ann_temp_rcp85_2060.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2056_2060_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2056_2060_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_0deg_2056_2060_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2056_2060_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2056_2060_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_3deg_2056_2060_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2056_2060_average_rcp26.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2056_2060_average_rcp45.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Sum_gdays_5deg_2056_2060_average_rcp85.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp26_2060.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp45_2060.tif</t>
+  </si>
+  <si>
+    <t>Data/Preds/Prepared/Layers/Climatic/Average_Avg_precip_rcp85_2060.tif</t>
   </si>
 </sst>
 </file>
@@ -11221,7 +11221,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B2" t="s">
         <v>1257</v>
@@ -11262,7 +11262,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B3" t="s">
         <v>1269</v>
@@ -11303,7 +11303,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B4" t="s">
         <v>1273</v>
@@ -11344,7 +11344,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B5" t="s">
         <v>1277</v>
@@ -11385,7 +11385,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B6" t="s">
         <v>1281</v>
@@ -11426,7 +11426,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B7" t="s">
         <v>1285</v>
@@ -11467,7 +11467,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B8" t="s">
         <v>1289</v>
@@ -11511,7 +11511,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B9" t="s">
         <v>1298</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B10" t="s">
         <v>1303</v>
@@ -11599,7 +11599,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B11" t="s">
         <v>1308</v>
@@ -11643,7 +11643,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B12" t="s">
         <v>1313</v>
@@ -11684,7 +11684,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B13" t="s">
         <v>1317</v>
@@ -11731,7 +11731,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B14" t="s">
         <v>1325</v>
@@ -11775,7 +11775,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B15" t="s">
         <v>1331</v>
@@ -11819,7 +11819,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B16" t="s">
         <v>1338</v>
@@ -11863,7 +11863,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B17" t="s">
         <v>1344</v>
@@ -11904,7 +11904,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B18" t="s">
         <v>1349</v>
@@ -11928,13 +11928,13 @@
         <v>1354</v>
       </c>
       <c r="K18" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M18" t="s">
         <v>1266</v>
       </c>
       <c r="O18" t="s">
-        <v>1558</v>
+        <v>1465</v>
       </c>
       <c r="P18" t="s">
         <v>1356</v>
@@ -11942,7 +11942,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B19" t="s">
         <v>1349</v>
@@ -11966,13 +11966,13 @@
         <v>1354</v>
       </c>
       <c r="K19" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M19" t="s">
         <v>1266</v>
       </c>
       <c r="O19" t="s">
-        <v>1559</v>
+        <v>1466</v>
       </c>
       <c r="P19" t="s">
         <v>1358</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B20" t="s">
         <v>1349</v>
@@ -12004,13 +12004,13 @@
         <v>1354</v>
       </c>
       <c r="K20" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M20" t="s">
         <v>1266</v>
       </c>
       <c r="O20" t="s">
-        <v>1560</v>
+        <v>1467</v>
       </c>
       <c r="P20" t="s">
         <v>1360</v>
@@ -12018,7 +12018,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B21" t="s">
         <v>1349</v>
@@ -12042,13 +12042,13 @@
         <v>1354</v>
       </c>
       <c r="K21" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M21" t="s">
         <v>1266</v>
       </c>
       <c r="O21" t="s">
-        <v>1561</v>
+        <v>1468</v>
       </c>
       <c r="P21" t="s">
         <v>1362</v>
@@ -12056,7 +12056,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B22" t="s">
         <v>1349</v>
@@ -12080,13 +12080,13 @@
         <v>1354</v>
       </c>
       <c r="K22" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M22" t="s">
         <v>1266</v>
       </c>
       <c r="O22" t="s">
-        <v>1562</v>
+        <v>1469</v>
       </c>
       <c r="P22" t="s">
         <v>1364</v>
@@ -12094,7 +12094,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B23" t="s">
         <v>1365</v>
@@ -12118,13 +12118,13 @@
         <v>1354</v>
       </c>
       <c r="K23" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M23" t="s">
         <v>1266</v>
       </c>
       <c r="O23" t="s">
-        <v>1563</v>
+        <v>1470</v>
       </c>
       <c r="P23" t="s">
         <v>1356</v>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B24" t="s">
         <v>1365</v>
@@ -12156,13 +12156,13 @@
         <v>1354</v>
       </c>
       <c r="K24" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M24" t="s">
         <v>1266</v>
       </c>
       <c r="O24" t="s">
-        <v>1564</v>
+        <v>1471</v>
       </c>
       <c r="P24" t="s">
         <v>1358</v>
@@ -12170,7 +12170,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B25" t="s">
         <v>1365</v>
@@ -12194,13 +12194,13 @@
         <v>1354</v>
       </c>
       <c r="K25" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M25" t="s">
         <v>1266</v>
       </c>
       <c r="O25" t="s">
-        <v>1565</v>
+        <v>1472</v>
       </c>
       <c r="P25" t="s">
         <v>1360</v>
@@ -12208,7 +12208,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B26" t="s">
         <v>1365</v>
@@ -12232,13 +12232,13 @@
         <v>1354</v>
       </c>
       <c r="K26" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M26" t="s">
         <v>1266</v>
       </c>
       <c r="O26" t="s">
-        <v>1566</v>
+        <v>1473</v>
       </c>
       <c r="P26" t="s">
         <v>1362</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B27" t="s">
         <v>1365</v>
@@ -12270,13 +12270,13 @@
         <v>1354</v>
       </c>
       <c r="K27" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M27" t="s">
         <v>1266</v>
       </c>
       <c r="O27" t="s">
-        <v>1567</v>
+        <v>1474</v>
       </c>
       <c r="P27" t="s">
         <v>1364</v>
@@ -12284,7 +12284,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B28" t="s">
         <v>1371</v>
@@ -12308,13 +12308,13 @@
         <v>1354</v>
       </c>
       <c r="K28" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M28" t="s">
         <v>1266</v>
       </c>
       <c r="O28" t="s">
-        <v>1568</v>
+        <v>1475</v>
       </c>
       <c r="P28" t="s">
         <v>1356</v>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B29" t="s">
         <v>1371</v>
@@ -12346,13 +12346,13 @@
         <v>1354</v>
       </c>
       <c r="K29" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M29" t="s">
         <v>1266</v>
       </c>
       <c r="O29" t="s">
-        <v>1569</v>
+        <v>1476</v>
       </c>
       <c r="P29" t="s">
         <v>1358</v>
@@ -12360,7 +12360,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B30" t="s">
         <v>1371</v>
@@ -12384,13 +12384,13 @@
         <v>1354</v>
       </c>
       <c r="K30" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M30" t="s">
         <v>1266</v>
       </c>
       <c r="O30" t="s">
-        <v>1570</v>
+        <v>1477</v>
       </c>
       <c r="P30" t="s">
         <v>1360</v>
@@ -12398,7 +12398,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B31" t="s">
         <v>1371</v>
@@ -12422,13 +12422,13 @@
         <v>1354</v>
       </c>
       <c r="K31" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M31" t="s">
         <v>1266</v>
       </c>
       <c r="O31" t="s">
-        <v>1571</v>
+        <v>1478</v>
       </c>
       <c r="P31" t="s">
         <v>1362</v>
@@ -12436,7 +12436,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B32" t="s">
         <v>1371</v>
@@ -12460,13 +12460,13 @@
         <v>1354</v>
       </c>
       <c r="K32" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M32" t="s">
         <v>1266</v>
       </c>
       <c r="O32" t="s">
-        <v>1572</v>
+        <v>1479</v>
       </c>
       <c r="P32" t="s">
         <v>1364</v>
@@ -12474,7 +12474,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B33" t="s">
         <v>1377</v>
@@ -12498,21 +12498,21 @@
         <v>1354</v>
       </c>
       <c r="K33" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M33" t="s">
         <v>1266</v>
       </c>
       <c r="O33" t="s">
-        <v>1573</v>
+        <v>1590</v>
       </c>
       <c r="P33" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B34" t="s">
         <v>1377</v>
@@ -12536,21 +12536,21 @@
         <v>1354</v>
       </c>
       <c r="K34" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M34" t="s">
         <v>1266</v>
       </c>
       <c r="O34" t="s">
-        <v>1574</v>
+        <v>1591</v>
       </c>
       <c r="P34" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B35" t="s">
         <v>1377</v>
@@ -12574,24 +12574,24 @@
         <v>1354</v>
       </c>
       <c r="K35" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M35" t="s">
         <v>1266</v>
       </c>
       <c r="O35" t="s">
-        <v>1575</v>
+        <v>1592</v>
       </c>
       <c r="P35" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B36" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D36" t="s">
         <v>1259</v>
@@ -12612,24 +12612,24 @@
         <v>1354</v>
       </c>
       <c r="K36" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M36" t="s">
         <v>1266</v>
       </c>
       <c r="O36" t="s">
-        <v>1576</v>
+        <v>1593</v>
       </c>
       <c r="P36" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B37" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="s">
         <v>1259</v>
@@ -12650,24 +12650,24 @@
         <v>1354</v>
       </c>
       <c r="K37" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M37" t="s">
         <v>1266</v>
       </c>
       <c r="O37" t="s">
-        <v>1577</v>
+        <v>1594</v>
       </c>
       <c r="P37" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B38" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D38" t="s">
         <v>1259</v>
@@ -12688,24 +12688,24 @@
         <v>1354</v>
       </c>
       <c r="K38" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M38" t="s">
         <v>1266</v>
       </c>
       <c r="O38" t="s">
-        <v>1578</v>
+        <v>1595</v>
       </c>
       <c r="P38" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B39" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D39" t="s">
         <v>1259</v>
@@ -12726,24 +12726,24 @@
         <v>1354</v>
       </c>
       <c r="K39" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M39" t="s">
         <v>1266</v>
       </c>
       <c r="O39" t="s">
-        <v>1579</v>
+        <v>1596</v>
       </c>
       <c r="P39" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B40" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D40" t="s">
         <v>1259</v>
@@ -12764,24 +12764,24 @@
         <v>1354</v>
       </c>
       <c r="K40" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M40" t="s">
         <v>1266</v>
       </c>
       <c r="O40" t="s">
-        <v>1580</v>
+        <v>1597</v>
       </c>
       <c r="P40" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B41" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D41" t="s">
         <v>1259</v>
@@ -12802,24 +12802,24 @@
         <v>1354</v>
       </c>
       <c r="K41" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M41" t="s">
         <v>1266</v>
       </c>
       <c r="O41" t="s">
-        <v>1581</v>
+        <v>1598</v>
       </c>
       <c r="P41" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B42" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D42" t="s">
         <v>1259</v>
@@ -12840,24 +12840,24 @@
         <v>1354</v>
       </c>
       <c r="K42" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M42" t="s">
         <v>1266</v>
       </c>
       <c r="O42" t="s">
-        <v>1582</v>
+        <v>1599</v>
       </c>
       <c r="P42" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B43" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D43" t="s">
         <v>1259</v>
@@ -12878,24 +12878,24 @@
         <v>1354</v>
       </c>
       <c r="K43" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M43" t="s">
         <v>1266</v>
       </c>
       <c r="O43" t="s">
-        <v>1583</v>
+        <v>1600</v>
       </c>
       <c r="P43" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B44" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D44" t="s">
         <v>1259</v>
@@ -12916,24 +12916,24 @@
         <v>1354</v>
       </c>
       <c r="K44" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M44" t="s">
         <v>1266</v>
       </c>
       <c r="O44" t="s">
-        <v>1584</v>
+        <v>1601</v>
       </c>
       <c r="P44" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B45" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D45" t="s">
         <v>1259</v>
@@ -12954,24 +12954,24 @@
         <v>1354</v>
       </c>
       <c r="K45" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M45" t="s">
         <v>1266</v>
       </c>
       <c r="O45" t="s">
-        <v>1585</v>
+        <v>1602</v>
       </c>
       <c r="P45" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B46" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D46" t="s">
         <v>1259</v>
@@ -12992,24 +12992,24 @@
         <v>1354</v>
       </c>
       <c r="K46" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M46" t="s">
         <v>1266</v>
       </c>
       <c r="O46" t="s">
-        <v>1586</v>
+        <v>1603</v>
       </c>
       <c r="P46" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="B47" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D47" t="s">
         <v>1259</v>
@@ -13030,16 +13030,16 @@
         <v>1354</v>
       </c>
       <c r="K47" t="s">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="M47" t="s">
         <v>1266</v>
       </c>
       <c r="O47" t="s">
-        <v>1587</v>
+        <v>1604</v>
       </c>
       <c r="P47" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
@@ -13105,7 +13105,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B2" t="s">
         <v>1257</v>
@@ -13146,7 +13146,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B3" t="s">
         <v>1269</v>
@@ -13187,7 +13187,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B4" t="s">
         <v>1273</v>
@@ -13228,7 +13228,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B5" t="s">
         <v>1277</v>
@@ -13269,7 +13269,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B6" t="s">
         <v>1281</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B7" t="s">
         <v>1285</v>
@@ -13351,7 +13351,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B8" t="s">
         <v>1289</v>
@@ -13395,7 +13395,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B9" t="s">
         <v>1298</v>
@@ -13439,7 +13439,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B10" t="s">
         <v>1303</v>
@@ -13483,7 +13483,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B11" t="s">
         <v>1308</v>
@@ -13527,7 +13527,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B12" t="s">
         <v>1313</v>
@@ -13568,7 +13568,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B13" t="s">
         <v>1317</v>
@@ -13615,7 +13615,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B14" t="s">
         <v>1325</v>
@@ -13659,7 +13659,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B15" t="s">
         <v>1331</v>
@@ -13703,7 +13703,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B16" t="s">
         <v>1338</v>
@@ -13747,7 +13747,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B17" t="s">
         <v>1344</v>
@@ -13788,7 +13788,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B18" t="s">
         <v>1349</v>
@@ -13812,13 +13812,13 @@
         <v>1354</v>
       </c>
       <c r="K18" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M18" t="s">
         <v>1266</v>
       </c>
       <c r="O18" t="s">
-        <v>1589</v>
+        <v>1481</v>
       </c>
       <c r="P18" t="s">
         <v>1356</v>
@@ -13826,7 +13826,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B19" t="s">
         <v>1349</v>
@@ -13850,13 +13850,13 @@
         <v>1354</v>
       </c>
       <c r="K19" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M19" t="s">
         <v>1266</v>
       </c>
       <c r="O19" t="s">
-        <v>1590</v>
+        <v>1482</v>
       </c>
       <c r="P19" t="s">
         <v>1358</v>
@@ -13864,7 +13864,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B20" t="s">
         <v>1349</v>
@@ -13888,13 +13888,13 @@
         <v>1354</v>
       </c>
       <c r="K20" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M20" t="s">
         <v>1266</v>
       </c>
       <c r="O20" t="s">
-        <v>1591</v>
+        <v>1483</v>
       </c>
       <c r="P20" t="s">
         <v>1360</v>
@@ -13902,7 +13902,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B21" t="s">
         <v>1349</v>
@@ -13926,13 +13926,13 @@
         <v>1354</v>
       </c>
       <c r="K21" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M21" t="s">
         <v>1266</v>
       </c>
       <c r="O21" t="s">
-        <v>1592</v>
+        <v>1484</v>
       </c>
       <c r="P21" t="s">
         <v>1362</v>
@@ -13940,7 +13940,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B22" t="s">
         <v>1349</v>
@@ -13964,13 +13964,13 @@
         <v>1354</v>
       </c>
       <c r="K22" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M22" t="s">
         <v>1266</v>
       </c>
       <c r="O22" t="s">
-        <v>1593</v>
+        <v>1485</v>
       </c>
       <c r="P22" t="s">
         <v>1364</v>
@@ -13978,7 +13978,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B23" t="s">
         <v>1365</v>
@@ -14002,13 +14002,13 @@
         <v>1354</v>
       </c>
       <c r="K23" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M23" t="s">
         <v>1266</v>
       </c>
       <c r="O23" t="s">
-        <v>1594</v>
+        <v>1486</v>
       </c>
       <c r="P23" t="s">
         <v>1356</v>
@@ -14016,7 +14016,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B24" t="s">
         <v>1365</v>
@@ -14040,13 +14040,13 @@
         <v>1354</v>
       </c>
       <c r="K24" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M24" t="s">
         <v>1266</v>
       </c>
       <c r="O24" t="s">
-        <v>1595</v>
+        <v>1487</v>
       </c>
       <c r="P24" t="s">
         <v>1358</v>
@@ -14054,7 +14054,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B25" t="s">
         <v>1365</v>
@@ -14078,13 +14078,13 @@
         <v>1354</v>
       </c>
       <c r="K25" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M25" t="s">
         <v>1266</v>
       </c>
       <c r="O25" t="s">
-        <v>1596</v>
+        <v>1488</v>
       </c>
       <c r="P25" t="s">
         <v>1360</v>
@@ -14092,7 +14092,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B26" t="s">
         <v>1365</v>
@@ -14116,13 +14116,13 @@
         <v>1354</v>
       </c>
       <c r="K26" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M26" t="s">
         <v>1266</v>
       </c>
       <c r="O26" t="s">
-        <v>1597</v>
+        <v>1489</v>
       </c>
       <c r="P26" t="s">
         <v>1362</v>
@@ -14130,7 +14130,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B27" t="s">
         <v>1365</v>
@@ -14154,13 +14154,13 @@
         <v>1354</v>
       </c>
       <c r="K27" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M27" t="s">
         <v>1266</v>
       </c>
       <c r="O27" t="s">
-        <v>1598</v>
+        <v>1490</v>
       </c>
       <c r="P27" t="s">
         <v>1364</v>
@@ -14168,7 +14168,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B28" t="s">
         <v>1371</v>
@@ -14192,13 +14192,13 @@
         <v>1354</v>
       </c>
       <c r="K28" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M28" t="s">
         <v>1266</v>
       </c>
       <c r="O28" t="s">
-        <v>1599</v>
+        <v>1491</v>
       </c>
       <c r="P28" t="s">
         <v>1356</v>
@@ -14206,7 +14206,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B29" t="s">
         <v>1371</v>
@@ -14230,13 +14230,13 @@
         <v>1354</v>
       </c>
       <c r="K29" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M29" t="s">
         <v>1266</v>
       </c>
       <c r="O29" t="s">
-        <v>1600</v>
+        <v>1492</v>
       </c>
       <c r="P29" t="s">
         <v>1358</v>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B30" t="s">
         <v>1371</v>
@@ -14268,13 +14268,13 @@
         <v>1354</v>
       </c>
       <c r="K30" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M30" t="s">
         <v>1266</v>
       </c>
       <c r="O30" t="s">
-        <v>1601</v>
+        <v>1493</v>
       </c>
       <c r="P30" t="s">
         <v>1360</v>
@@ -14282,7 +14282,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B31" t="s">
         <v>1371</v>
@@ -14306,13 +14306,13 @@
         <v>1354</v>
       </c>
       <c r="K31" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M31" t="s">
         <v>1266</v>
       </c>
       <c r="O31" t="s">
-        <v>1602</v>
+        <v>1494</v>
       </c>
       <c r="P31" t="s">
         <v>1362</v>
@@ -14320,7 +14320,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B32" t="s">
         <v>1371</v>
@@ -14344,13 +14344,13 @@
         <v>1354</v>
       </c>
       <c r="K32" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M32" t="s">
         <v>1266</v>
       </c>
       <c r="O32" t="s">
-        <v>1603</v>
+        <v>1495</v>
       </c>
       <c r="P32" t="s">
         <v>1364</v>
@@ -14358,7 +14358,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B33" t="s">
         <v>1377</v>
@@ -14382,21 +14382,21 @@
         <v>1354</v>
       </c>
       <c r="K33" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M33" t="s">
         <v>1266</v>
       </c>
       <c r="O33" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="P33" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B34" t="s">
         <v>1377</v>
@@ -14420,21 +14420,21 @@
         <v>1354</v>
       </c>
       <c r="K34" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M34" t="s">
         <v>1266</v>
       </c>
       <c r="O34" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="P34" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B35" t="s">
         <v>1377</v>
@@ -14458,24 +14458,24 @@
         <v>1354</v>
       </c>
       <c r="K35" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M35" t="s">
         <v>1266</v>
       </c>
       <c r="O35" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="P35" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B36" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D36" t="s">
         <v>1259</v>
@@ -14496,24 +14496,24 @@
         <v>1354</v>
       </c>
       <c r="K36" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M36" t="s">
         <v>1266</v>
       </c>
       <c r="O36" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="P36" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B37" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="s">
         <v>1259</v>
@@ -14534,24 +14534,24 @@
         <v>1354</v>
       </c>
       <c r="K37" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M37" t="s">
         <v>1266</v>
       </c>
       <c r="O37" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="P37" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B38" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D38" t="s">
         <v>1259</v>
@@ -14572,24 +14572,24 @@
         <v>1354</v>
       </c>
       <c r="K38" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M38" t="s">
         <v>1266</v>
       </c>
       <c r="O38" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="P38" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B39" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D39" t="s">
         <v>1259</v>
@@ -14610,24 +14610,24 @@
         <v>1354</v>
       </c>
       <c r="K39" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M39" t="s">
         <v>1266</v>
       </c>
       <c r="O39" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="P39" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B40" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D40" t="s">
         <v>1259</v>
@@ -14648,24 +14648,24 @@
         <v>1354</v>
       </c>
       <c r="K40" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M40" t="s">
         <v>1266</v>
       </c>
       <c r="O40" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="P40" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B41" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D41" t="s">
         <v>1259</v>
@@ -14686,24 +14686,24 @@
         <v>1354</v>
       </c>
       <c r="K41" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M41" t="s">
         <v>1266</v>
       </c>
       <c r="O41" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="P41" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B42" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D42" t="s">
         <v>1259</v>
@@ -14724,24 +14724,24 @@
         <v>1354</v>
       </c>
       <c r="K42" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M42" t="s">
         <v>1266</v>
       </c>
       <c r="O42" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="P42" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B43" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D43" t="s">
         <v>1259</v>
@@ -14762,24 +14762,24 @@
         <v>1354</v>
       </c>
       <c r="K43" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M43" t="s">
         <v>1266</v>
       </c>
       <c r="O43" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="P43" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B44" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D44" t="s">
         <v>1259</v>
@@ -14800,24 +14800,24 @@
         <v>1354</v>
       </c>
       <c r="K44" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M44" t="s">
         <v>1266</v>
       </c>
       <c r="O44" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="P44" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B45" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D45" t="s">
         <v>1259</v>
@@ -14838,24 +14838,24 @@
         <v>1354</v>
       </c>
       <c r="K45" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M45" t="s">
         <v>1266</v>
       </c>
       <c r="O45" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="P45" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B46" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D46" t="s">
         <v>1259</v>
@@ -14876,24 +14876,24 @@
         <v>1354</v>
       </c>
       <c r="K46" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M46" t="s">
         <v>1266</v>
       </c>
       <c r="O46" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="P46" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="B47" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D47" t="s">
         <v>1259</v>
@@ -14914,16 +14914,16 @@
         <v>1354</v>
       </c>
       <c r="K47" t="s">
-        <v>1588</v>
+        <v>1480</v>
       </c>
       <c r="M47" t="s">
         <v>1266</v>
       </c>
       <c r="O47" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="P47" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
@@ -14989,7 +14989,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B2" t="s">
         <v>1257</v>
@@ -15030,7 +15030,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B3" t="s">
         <v>1269</v>
@@ -15071,7 +15071,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B4" t="s">
         <v>1273</v>
@@ -15112,7 +15112,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B5" t="s">
         <v>1277</v>
@@ -15153,7 +15153,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B6" t="s">
         <v>1281</v>
@@ -15194,7 +15194,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B7" t="s">
         <v>1285</v>
@@ -15235,7 +15235,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B8" t="s">
         <v>1289</v>
@@ -15279,7 +15279,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B9" t="s">
         <v>1298</v>
@@ -15323,7 +15323,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B10" t="s">
         <v>1303</v>
@@ -15367,7 +15367,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B11" t="s">
         <v>1308</v>
@@ -15411,7 +15411,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B12" t="s">
         <v>1313</v>
@@ -15452,7 +15452,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B13" t="s">
         <v>1317</v>
@@ -15499,7 +15499,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B14" t="s">
         <v>1325</v>
@@ -15543,7 +15543,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B15" t="s">
         <v>1331</v>
@@ -15587,7 +15587,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B16" t="s">
         <v>1338</v>
@@ -15631,7 +15631,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B17" t="s">
         <v>1344</v>
@@ -15672,7 +15672,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B18" t="s">
         <v>1377</v>
@@ -15696,7 +15696,7 @@
         <v>1354</v>
       </c>
       <c r="K18" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M18" t="s">
         <v>1266</v>
@@ -15705,12 +15705,12 @@
         <v>1620</v>
       </c>
       <c r="P18" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B19" t="s">
         <v>1377</v>
@@ -15734,7 +15734,7 @@
         <v>1354</v>
       </c>
       <c r="K19" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M19" t="s">
         <v>1266</v>
@@ -15743,12 +15743,12 @@
         <v>1621</v>
       </c>
       <c r="P19" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B20" t="s">
         <v>1377</v>
@@ -15772,7 +15772,7 @@
         <v>1354</v>
       </c>
       <c r="K20" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M20" t="s">
         <v>1266</v>
@@ -15781,15 +15781,15 @@
         <v>1622</v>
       </c>
       <c r="P20" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B21" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D21" t="s">
         <v>1259</v>
@@ -15810,7 +15810,7 @@
         <v>1354</v>
       </c>
       <c r="K21" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M21" t="s">
         <v>1266</v>
@@ -15819,15 +15819,15 @@
         <v>1623</v>
       </c>
       <c r="P21" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B22" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D22" t="s">
         <v>1259</v>
@@ -15848,7 +15848,7 @@
         <v>1354</v>
       </c>
       <c r="K22" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M22" t="s">
         <v>1266</v>
@@ -15857,15 +15857,15 @@
         <v>1624</v>
       </c>
       <c r="P22" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B23" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D23" t="s">
         <v>1259</v>
@@ -15886,7 +15886,7 @@
         <v>1354</v>
       </c>
       <c r="K23" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M23" t="s">
         <v>1266</v>
@@ -15895,15 +15895,15 @@
         <v>1625</v>
       </c>
       <c r="P23" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B24" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D24" t="s">
         <v>1259</v>
@@ -15924,7 +15924,7 @@
         <v>1354</v>
       </c>
       <c r="K24" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M24" t="s">
         <v>1266</v>
@@ -15933,15 +15933,15 @@
         <v>1626</v>
       </c>
       <c r="P24" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B25" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D25" t="s">
         <v>1259</v>
@@ -15962,7 +15962,7 @@
         <v>1354</v>
       </c>
       <c r="K25" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M25" t="s">
         <v>1266</v>
@@ -15971,15 +15971,15 @@
         <v>1627</v>
       </c>
       <c r="P25" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B26" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D26" t="s">
         <v>1259</v>
@@ -16000,7 +16000,7 @@
         <v>1354</v>
       </c>
       <c r="K26" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M26" t="s">
         <v>1266</v>
@@ -16009,15 +16009,15 @@
         <v>1628</v>
       </c>
       <c r="P26" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B27" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D27" t="s">
         <v>1259</v>
@@ -16038,7 +16038,7 @@
         <v>1354</v>
       </c>
       <c r="K27" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M27" t="s">
         <v>1266</v>
@@ -16047,15 +16047,15 @@
         <v>1629</v>
       </c>
       <c r="P27" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B28" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D28" t="s">
         <v>1259</v>
@@ -16076,7 +16076,7 @@
         <v>1354</v>
       </c>
       <c r="K28" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M28" t="s">
         <v>1266</v>
@@ -16085,15 +16085,15 @@
         <v>1630</v>
       </c>
       <c r="P28" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B29" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D29" t="s">
         <v>1259</v>
@@ -16114,7 +16114,7 @@
         <v>1354</v>
       </c>
       <c r="K29" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M29" t="s">
         <v>1266</v>
@@ -16123,15 +16123,15 @@
         <v>1631</v>
       </c>
       <c r="P29" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B30" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D30" t="s">
         <v>1259</v>
@@ -16152,7 +16152,7 @@
         <v>1354</v>
       </c>
       <c r="K30" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M30" t="s">
         <v>1266</v>
@@ -16161,15 +16161,15 @@
         <v>1632</v>
       </c>
       <c r="P30" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B31" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D31" t="s">
         <v>1259</v>
@@ -16190,7 +16190,7 @@
         <v>1354</v>
       </c>
       <c r="K31" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M31" t="s">
         <v>1266</v>
@@ -16199,15 +16199,15 @@
         <v>1633</v>
       </c>
       <c r="P31" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="B32" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D32" t="s">
         <v>1259</v>
@@ -16228,7 +16228,7 @@
         <v>1354</v>
       </c>
       <c r="K32" t="s">
-        <v>1619</v>
+        <v>1496</v>
       </c>
       <c r="M32" t="s">
         <v>1266</v>
@@ -16237,7 +16237,7 @@
         <v>1634</v>
       </c>
       <c r="P32" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
@@ -29312,10 +29312,10 @@
         <v>1266</v>
       </c>
       <c r="O33" t="s">
-        <v>1380</v>
+        <v>1497</v>
       </c>
       <c r="P33" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -29350,10 +29350,10 @@
         <v>1266</v>
       </c>
       <c r="O34" t="s">
-        <v>1382</v>
+        <v>1499</v>
       </c>
       <c r="P34" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -29388,10 +29388,10 @@
         <v>1266</v>
       </c>
       <c r="O35" t="s">
-        <v>1384</v>
+        <v>1501</v>
       </c>
       <c r="P35" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -29399,7 +29399,7 @@
         <v>1256</v>
       </c>
       <c r="B36" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D36" t="s">
         <v>1259</v>
@@ -29426,10 +29426,10 @@
         <v>1266</v>
       </c>
       <c r="O36" t="s">
-        <v>1387</v>
+        <v>1503</v>
       </c>
       <c r="P36" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -29437,7 +29437,7 @@
         <v>1256</v>
       </c>
       <c r="B37" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="s">
         <v>1259</v>
@@ -29464,10 +29464,10 @@
         <v>1266</v>
       </c>
       <c r="O37" t="s">
-        <v>1388</v>
+        <v>1504</v>
       </c>
       <c r="P37" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -29475,7 +29475,7 @@
         <v>1256</v>
       </c>
       <c r="B38" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D38" t="s">
         <v>1259</v>
@@ -29502,10 +29502,10 @@
         <v>1266</v>
       </c>
       <c r="O38" t="s">
-        <v>1389</v>
+        <v>1505</v>
       </c>
       <c r="P38" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -29513,7 +29513,7 @@
         <v>1256</v>
       </c>
       <c r="B39" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D39" t="s">
         <v>1259</v>
@@ -29540,10 +29540,10 @@
         <v>1266</v>
       </c>
       <c r="O39" t="s">
-        <v>1391</v>
+        <v>1506</v>
       </c>
       <c r="P39" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -29551,7 +29551,7 @@
         <v>1256</v>
       </c>
       <c r="B40" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D40" t="s">
         <v>1259</v>
@@ -29578,10 +29578,10 @@
         <v>1266</v>
       </c>
       <c r="O40" t="s">
-        <v>1392</v>
+        <v>1507</v>
       </c>
       <c r="P40" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -29589,7 +29589,7 @@
         <v>1256</v>
       </c>
       <c r="B41" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D41" t="s">
         <v>1259</v>
@@ -29616,10 +29616,10 @@
         <v>1266</v>
       </c>
       <c r="O41" t="s">
-        <v>1393</v>
+        <v>1508</v>
       </c>
       <c r="P41" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -29627,7 +29627,7 @@
         <v>1256</v>
       </c>
       <c r="B42" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D42" t="s">
         <v>1259</v>
@@ -29654,10 +29654,10 @@
         <v>1266</v>
       </c>
       <c r="O42" t="s">
-        <v>1395</v>
+        <v>1509</v>
       </c>
       <c r="P42" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -29665,7 +29665,7 @@
         <v>1256</v>
       </c>
       <c r="B43" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D43" t="s">
         <v>1259</v>
@@ -29692,10 +29692,10 @@
         <v>1266</v>
       </c>
       <c r="O43" t="s">
-        <v>1396</v>
+        <v>1510</v>
       </c>
       <c r="P43" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -29703,7 +29703,7 @@
         <v>1256</v>
       </c>
       <c r="B44" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D44" t="s">
         <v>1259</v>
@@ -29730,10 +29730,10 @@
         <v>1266</v>
       </c>
       <c r="O44" t="s">
-        <v>1397</v>
+        <v>1511</v>
       </c>
       <c r="P44" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -29741,7 +29741,7 @@
         <v>1256</v>
       </c>
       <c r="B45" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D45" t="s">
         <v>1259</v>
@@ -29768,10 +29768,10 @@
         <v>1266</v>
       </c>
       <c r="O45" t="s">
-        <v>1399</v>
+        <v>1512</v>
       </c>
       <c r="P45" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -29779,7 +29779,7 @@
         <v>1256</v>
       </c>
       <c r="B46" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D46" t="s">
         <v>1259</v>
@@ -29806,10 +29806,10 @@
         <v>1266</v>
       </c>
       <c r="O46" t="s">
-        <v>1400</v>
+        <v>1513</v>
       </c>
       <c r="P46" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -29817,7 +29817,7 @@
         <v>1256</v>
       </c>
       <c r="B47" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D47" t="s">
         <v>1259</v>
@@ -29844,10 +29844,10 @@
         <v>1266</v>
       </c>
       <c r="O47" t="s">
-        <v>1401</v>
+        <v>1514</v>
       </c>
       <c r="P47" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
@@ -29913,7 +29913,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B2" t="s">
         <v>1257</v>
@@ -29954,7 +29954,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B3" t="s">
         <v>1269</v>
@@ -29995,7 +29995,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B4" t="s">
         <v>1273</v>
@@ -30036,7 +30036,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B5" t="s">
         <v>1277</v>
@@ -30077,7 +30077,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B6" t="s">
         <v>1281</v>
@@ -30118,7 +30118,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B7" t="s">
         <v>1285</v>
@@ -30159,7 +30159,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B8" t="s">
         <v>1289</v>
@@ -30203,7 +30203,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B9" t="s">
         <v>1298</v>
@@ -30247,7 +30247,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B10" t="s">
         <v>1303</v>
@@ -30291,7 +30291,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B11" t="s">
         <v>1308</v>
@@ -30335,7 +30335,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B12" t="s">
         <v>1313</v>
@@ -30376,7 +30376,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B13" t="s">
         <v>1317</v>
@@ -30423,7 +30423,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B14" t="s">
         <v>1325</v>
@@ -30467,7 +30467,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B15" t="s">
         <v>1331</v>
@@ -30511,7 +30511,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B16" t="s">
         <v>1338</v>
@@ -30555,7 +30555,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B17" t="s">
         <v>1344</v>
@@ -30596,7 +30596,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B18" t="s">
         <v>1349</v>
@@ -30620,13 +30620,13 @@
         <v>1354</v>
       </c>
       <c r="K18" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M18" t="s">
         <v>1266</v>
       </c>
       <c r="O18" t="s">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="P18" t="s">
         <v>1356</v>
@@ -30634,7 +30634,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B19" t="s">
         <v>1349</v>
@@ -30658,13 +30658,13 @@
         <v>1354</v>
       </c>
       <c r="K19" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M19" t="s">
         <v>1266</v>
       </c>
       <c r="O19" t="s">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="P19" t="s">
         <v>1358</v>
@@ -30672,7 +30672,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B20" t="s">
         <v>1349</v>
@@ -30696,13 +30696,13 @@
         <v>1354</v>
       </c>
       <c r="K20" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M20" t="s">
         <v>1266</v>
       </c>
       <c r="O20" t="s">
-        <v>1405</v>
+        <v>1387</v>
       </c>
       <c r="P20" t="s">
         <v>1360</v>
@@ -30710,7 +30710,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B21" t="s">
         <v>1349</v>
@@ -30734,13 +30734,13 @@
         <v>1354</v>
       </c>
       <c r="K21" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M21" t="s">
         <v>1266</v>
       </c>
       <c r="O21" t="s">
-        <v>1406</v>
+        <v>1388</v>
       </c>
       <c r="P21" t="s">
         <v>1362</v>
@@ -30748,7 +30748,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B22" t="s">
         <v>1349</v>
@@ -30772,13 +30772,13 @@
         <v>1354</v>
       </c>
       <c r="K22" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M22" t="s">
         <v>1266</v>
       </c>
       <c r="O22" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="P22" t="s">
         <v>1364</v>
@@ -30786,7 +30786,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B23" t="s">
         <v>1365</v>
@@ -30810,13 +30810,13 @@
         <v>1354</v>
       </c>
       <c r="K23" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M23" t="s">
         <v>1266</v>
       </c>
       <c r="O23" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="P23" t="s">
         <v>1356</v>
@@ -30824,7 +30824,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B24" t="s">
         <v>1365</v>
@@ -30848,13 +30848,13 @@
         <v>1354</v>
       </c>
       <c r="K24" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M24" t="s">
         <v>1266</v>
       </c>
       <c r="O24" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="P24" t="s">
         <v>1358</v>
@@ -30862,7 +30862,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B25" t="s">
         <v>1365</v>
@@ -30886,13 +30886,13 @@
         <v>1354</v>
       </c>
       <c r="K25" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M25" t="s">
         <v>1266</v>
       </c>
       <c r="O25" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="P25" t="s">
         <v>1360</v>
@@ -30900,7 +30900,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B26" t="s">
         <v>1365</v>
@@ -30924,13 +30924,13 @@
         <v>1354</v>
       </c>
       <c r="K26" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M26" t="s">
         <v>1266</v>
       </c>
       <c r="O26" t="s">
-        <v>1411</v>
+        <v>1393</v>
       </c>
       <c r="P26" t="s">
         <v>1362</v>
@@ -30938,7 +30938,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B27" t="s">
         <v>1365</v>
@@ -30962,13 +30962,13 @@
         <v>1354</v>
       </c>
       <c r="K27" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M27" t="s">
         <v>1266</v>
       </c>
       <c r="O27" t="s">
-        <v>1412</v>
+        <v>1394</v>
       </c>
       <c r="P27" t="s">
         <v>1364</v>
@@ -30976,7 +30976,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B28" t="s">
         <v>1371</v>
@@ -31000,13 +31000,13 @@
         <v>1354</v>
       </c>
       <c r="K28" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M28" t="s">
         <v>1266</v>
       </c>
       <c r="O28" t="s">
-        <v>1413</v>
+        <v>1395</v>
       </c>
       <c r="P28" t="s">
         <v>1356</v>
@@ -31014,7 +31014,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B29" t="s">
         <v>1371</v>
@@ -31038,13 +31038,13 @@
         <v>1354</v>
       </c>
       <c r="K29" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M29" t="s">
         <v>1266</v>
       </c>
       <c r="O29" t="s">
-        <v>1414</v>
+        <v>1396</v>
       </c>
       <c r="P29" t="s">
         <v>1358</v>
@@ -31052,7 +31052,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B30" t="s">
         <v>1371</v>
@@ -31076,13 +31076,13 @@
         <v>1354</v>
       </c>
       <c r="K30" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M30" t="s">
         <v>1266</v>
       </c>
       <c r="O30" t="s">
-        <v>1415</v>
+        <v>1397</v>
       </c>
       <c r="P30" t="s">
         <v>1360</v>
@@ -31090,7 +31090,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B31" t="s">
         <v>1371</v>
@@ -31114,13 +31114,13 @@
         <v>1354</v>
       </c>
       <c r="K31" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M31" t="s">
         <v>1266</v>
       </c>
       <c r="O31" t="s">
-        <v>1416</v>
+        <v>1398</v>
       </c>
       <c r="P31" t="s">
         <v>1362</v>
@@ -31128,7 +31128,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B32" t="s">
         <v>1371</v>
@@ -31152,13 +31152,13 @@
         <v>1354</v>
       </c>
       <c r="K32" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M32" t="s">
         <v>1266</v>
       </c>
       <c r="O32" t="s">
-        <v>1417</v>
+        <v>1399</v>
       </c>
       <c r="P32" t="s">
         <v>1364</v>
@@ -31166,7 +31166,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B33" t="s">
         <v>1377</v>
@@ -31190,21 +31190,21 @@
         <v>1354</v>
       </c>
       <c r="K33" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M33" t="s">
         <v>1266</v>
       </c>
       <c r="O33" t="s">
-        <v>1418</v>
+        <v>1515</v>
       </c>
       <c r="P33" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B34" t="s">
         <v>1377</v>
@@ -31228,21 +31228,21 @@
         <v>1354</v>
       </c>
       <c r="K34" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M34" t="s">
         <v>1266</v>
       </c>
       <c r="O34" t="s">
-        <v>1419</v>
+        <v>1516</v>
       </c>
       <c r="P34" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B35" t="s">
         <v>1377</v>
@@ -31266,24 +31266,24 @@
         <v>1354</v>
       </c>
       <c r="K35" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M35" t="s">
         <v>1266</v>
       </c>
       <c r="O35" t="s">
-        <v>1420</v>
+        <v>1517</v>
       </c>
       <c r="P35" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B36" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D36" t="s">
         <v>1259</v>
@@ -31304,24 +31304,24 @@
         <v>1354</v>
       </c>
       <c r="K36" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M36" t="s">
         <v>1266</v>
       </c>
       <c r="O36" t="s">
-        <v>1421</v>
+        <v>1518</v>
       </c>
       <c r="P36" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B37" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="s">
         <v>1259</v>
@@ -31342,24 +31342,24 @@
         <v>1354</v>
       </c>
       <c r="K37" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M37" t="s">
         <v>1266</v>
       </c>
       <c r="O37" t="s">
-        <v>1422</v>
+        <v>1519</v>
       </c>
       <c r="P37" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B38" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D38" t="s">
         <v>1259</v>
@@ -31380,24 +31380,24 @@
         <v>1354</v>
       </c>
       <c r="K38" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M38" t="s">
         <v>1266</v>
       </c>
       <c r="O38" t="s">
-        <v>1423</v>
+        <v>1520</v>
       </c>
       <c r="P38" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B39" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D39" t="s">
         <v>1259</v>
@@ -31418,24 +31418,24 @@
         <v>1354</v>
       </c>
       <c r="K39" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M39" t="s">
         <v>1266</v>
       </c>
       <c r="O39" t="s">
-        <v>1424</v>
+        <v>1521</v>
       </c>
       <c r="P39" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B40" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D40" t="s">
         <v>1259</v>
@@ -31456,24 +31456,24 @@
         <v>1354</v>
       </c>
       <c r="K40" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M40" t="s">
         <v>1266</v>
       </c>
       <c r="O40" t="s">
-        <v>1425</v>
+        <v>1522</v>
       </c>
       <c r="P40" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B41" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D41" t="s">
         <v>1259</v>
@@ -31494,24 +31494,24 @@
         <v>1354</v>
       </c>
       <c r="K41" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M41" t="s">
         <v>1266</v>
       </c>
       <c r="O41" t="s">
-        <v>1426</v>
+        <v>1523</v>
       </c>
       <c r="P41" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B42" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D42" t="s">
         <v>1259</v>
@@ -31532,24 +31532,24 @@
         <v>1354</v>
       </c>
       <c r="K42" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M42" t="s">
         <v>1266</v>
       </c>
       <c r="O42" t="s">
-        <v>1427</v>
+        <v>1524</v>
       </c>
       <c r="P42" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B43" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D43" t="s">
         <v>1259</v>
@@ -31570,24 +31570,24 @@
         <v>1354</v>
       </c>
       <c r="K43" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M43" t="s">
         <v>1266</v>
       </c>
       <c r="O43" t="s">
-        <v>1428</v>
+        <v>1525</v>
       </c>
       <c r="P43" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B44" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D44" t="s">
         <v>1259</v>
@@ -31608,24 +31608,24 @@
         <v>1354</v>
       </c>
       <c r="K44" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M44" t="s">
         <v>1266</v>
       </c>
       <c r="O44" t="s">
-        <v>1429</v>
+        <v>1526</v>
       </c>
       <c r="P44" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B45" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D45" t="s">
         <v>1259</v>
@@ -31646,24 +31646,24 @@
         <v>1354</v>
       </c>
       <c r="K45" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M45" t="s">
         <v>1266</v>
       </c>
       <c r="O45" t="s">
-        <v>1430</v>
+        <v>1527</v>
       </c>
       <c r="P45" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B46" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D46" t="s">
         <v>1259</v>
@@ -31684,24 +31684,24 @@
         <v>1354</v>
       </c>
       <c r="K46" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M46" t="s">
         <v>1266</v>
       </c>
       <c r="O46" t="s">
-        <v>1431</v>
+        <v>1528</v>
       </c>
       <c r="P46" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="B47" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D47" t="s">
         <v>1259</v>
@@ -31722,16 +31722,16 @@
         <v>1354</v>
       </c>
       <c r="K47" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="M47" t="s">
         <v>1266</v>
       </c>
       <c r="O47" t="s">
-        <v>1432</v>
+        <v>1529</v>
       </c>
       <c r="P47" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
@@ -31797,7 +31797,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B2" t="s">
         <v>1257</v>
@@ -31838,7 +31838,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B3" t="s">
         <v>1269</v>
@@ -31879,7 +31879,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B4" t="s">
         <v>1273</v>
@@ -31920,7 +31920,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B5" t="s">
         <v>1277</v>
@@ -31961,7 +31961,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B6" t="s">
         <v>1281</v>
@@ -32002,7 +32002,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B7" t="s">
         <v>1285</v>
@@ -32043,7 +32043,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B8" t="s">
         <v>1289</v>
@@ -32087,7 +32087,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B9" t="s">
         <v>1298</v>
@@ -32131,7 +32131,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B10" t="s">
         <v>1303</v>
@@ -32175,7 +32175,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B11" t="s">
         <v>1308</v>
@@ -32219,7 +32219,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B12" t="s">
         <v>1313</v>
@@ -32260,7 +32260,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B13" t="s">
         <v>1317</v>
@@ -32307,7 +32307,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B14" t="s">
         <v>1325</v>
@@ -32351,7 +32351,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B15" t="s">
         <v>1331</v>
@@ -32395,7 +32395,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B16" t="s">
         <v>1338</v>
@@ -32439,7 +32439,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B17" t="s">
         <v>1344</v>
@@ -32480,7 +32480,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B18" t="s">
         <v>1349</v>
@@ -32504,13 +32504,13 @@
         <v>1354</v>
       </c>
       <c r="K18" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M18" t="s">
         <v>1266</v>
       </c>
       <c r="O18" t="s">
-        <v>1434</v>
+        <v>1401</v>
       </c>
       <c r="P18" t="s">
         <v>1356</v>
@@ -32518,7 +32518,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B19" t="s">
         <v>1349</v>
@@ -32542,13 +32542,13 @@
         <v>1354</v>
       </c>
       <c r="K19" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M19" t="s">
         <v>1266</v>
       </c>
       <c r="O19" t="s">
-        <v>1435</v>
+        <v>1402</v>
       </c>
       <c r="P19" t="s">
         <v>1358</v>
@@ -32556,7 +32556,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B20" t="s">
         <v>1349</v>
@@ -32580,13 +32580,13 @@
         <v>1354</v>
       </c>
       <c r="K20" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M20" t="s">
         <v>1266</v>
       </c>
       <c r="O20" t="s">
-        <v>1436</v>
+        <v>1403</v>
       </c>
       <c r="P20" t="s">
         <v>1360</v>
@@ -32594,7 +32594,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B21" t="s">
         <v>1349</v>
@@ -32618,13 +32618,13 @@
         <v>1354</v>
       </c>
       <c r="K21" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M21" t="s">
         <v>1266</v>
       </c>
       <c r="O21" t="s">
-        <v>1437</v>
+        <v>1404</v>
       </c>
       <c r="P21" t="s">
         <v>1362</v>
@@ -32632,7 +32632,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B22" t="s">
         <v>1349</v>
@@ -32656,13 +32656,13 @@
         <v>1354</v>
       </c>
       <c r="K22" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M22" t="s">
         <v>1266</v>
       </c>
       <c r="O22" t="s">
-        <v>1438</v>
+        <v>1405</v>
       </c>
       <c r="P22" t="s">
         <v>1364</v>
@@ -32670,7 +32670,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B23" t="s">
         <v>1365</v>
@@ -32694,13 +32694,13 @@
         <v>1354</v>
       </c>
       <c r="K23" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M23" t="s">
         <v>1266</v>
       </c>
       <c r="O23" t="s">
-        <v>1439</v>
+        <v>1406</v>
       </c>
       <c r="P23" t="s">
         <v>1356</v>
@@ -32708,7 +32708,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B24" t="s">
         <v>1365</v>
@@ -32732,13 +32732,13 @@
         <v>1354</v>
       </c>
       <c r="K24" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M24" t="s">
         <v>1266</v>
       </c>
       <c r="O24" t="s">
-        <v>1440</v>
+        <v>1407</v>
       </c>
       <c r="P24" t="s">
         <v>1358</v>
@@ -32746,7 +32746,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B25" t="s">
         <v>1365</v>
@@ -32770,13 +32770,13 @@
         <v>1354</v>
       </c>
       <c r="K25" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M25" t="s">
         <v>1266</v>
       </c>
       <c r="O25" t="s">
-        <v>1441</v>
+        <v>1408</v>
       </c>
       <c r="P25" t="s">
         <v>1360</v>
@@ -32784,7 +32784,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B26" t="s">
         <v>1365</v>
@@ -32808,13 +32808,13 @@
         <v>1354</v>
       </c>
       <c r="K26" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M26" t="s">
         <v>1266</v>
       </c>
       <c r="O26" t="s">
-        <v>1442</v>
+        <v>1409</v>
       </c>
       <c r="P26" t="s">
         <v>1362</v>
@@ -32822,7 +32822,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B27" t="s">
         <v>1365</v>
@@ -32846,13 +32846,13 @@
         <v>1354</v>
       </c>
       <c r="K27" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M27" t="s">
         <v>1266</v>
       </c>
       <c r="O27" t="s">
-        <v>1443</v>
+        <v>1410</v>
       </c>
       <c r="P27" t="s">
         <v>1364</v>
@@ -32860,7 +32860,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B28" t="s">
         <v>1371</v>
@@ -32884,13 +32884,13 @@
         <v>1354</v>
       </c>
       <c r="K28" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M28" t="s">
         <v>1266</v>
       </c>
       <c r="O28" t="s">
-        <v>1444</v>
+        <v>1411</v>
       </c>
       <c r="P28" t="s">
         <v>1356</v>
@@ -32898,7 +32898,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B29" t="s">
         <v>1371</v>
@@ -32922,13 +32922,13 @@
         <v>1354</v>
       </c>
       <c r="K29" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M29" t="s">
         <v>1266</v>
       </c>
       <c r="O29" t="s">
-        <v>1445</v>
+        <v>1412</v>
       </c>
       <c r="P29" t="s">
         <v>1358</v>
@@ -32936,7 +32936,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B30" t="s">
         <v>1371</v>
@@ -32960,13 +32960,13 @@
         <v>1354</v>
       </c>
       <c r="K30" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M30" t="s">
         <v>1266</v>
       </c>
       <c r="O30" t="s">
-        <v>1446</v>
+        <v>1413</v>
       </c>
       <c r="P30" t="s">
         <v>1360</v>
@@ -32974,7 +32974,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B31" t="s">
         <v>1371</v>
@@ -32998,13 +32998,13 @@
         <v>1354</v>
       </c>
       <c r="K31" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M31" t="s">
         <v>1266</v>
       </c>
       <c r="O31" t="s">
-        <v>1447</v>
+        <v>1414</v>
       </c>
       <c r="P31" t="s">
         <v>1362</v>
@@ -33012,7 +33012,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B32" t="s">
         <v>1371</v>
@@ -33036,13 +33036,13 @@
         <v>1354</v>
       </c>
       <c r="K32" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M32" t="s">
         <v>1266</v>
       </c>
       <c r="O32" t="s">
-        <v>1448</v>
+        <v>1415</v>
       </c>
       <c r="P32" t="s">
         <v>1364</v>
@@ -33050,7 +33050,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B33" t="s">
         <v>1377</v>
@@ -33074,21 +33074,21 @@
         <v>1354</v>
       </c>
       <c r="K33" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M33" t="s">
         <v>1266</v>
       </c>
       <c r="O33" t="s">
-        <v>1449</v>
+        <v>1530</v>
       </c>
       <c r="P33" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B34" t="s">
         <v>1377</v>
@@ -33112,21 +33112,21 @@
         <v>1354</v>
       </c>
       <c r="K34" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M34" t="s">
         <v>1266</v>
       </c>
       <c r="O34" t="s">
-        <v>1450</v>
+        <v>1531</v>
       </c>
       <c r="P34" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B35" t="s">
         <v>1377</v>
@@ -33150,24 +33150,24 @@
         <v>1354</v>
       </c>
       <c r="K35" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M35" t="s">
         <v>1266</v>
       </c>
       <c r="O35" t="s">
-        <v>1451</v>
+        <v>1532</v>
       </c>
       <c r="P35" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B36" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D36" t="s">
         <v>1259</v>
@@ -33188,24 +33188,24 @@
         <v>1354</v>
       </c>
       <c r="K36" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M36" t="s">
         <v>1266</v>
       </c>
       <c r="O36" t="s">
-        <v>1452</v>
+        <v>1533</v>
       </c>
       <c r="P36" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B37" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="s">
         <v>1259</v>
@@ -33226,24 +33226,24 @@
         <v>1354</v>
       </c>
       <c r="K37" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M37" t="s">
         <v>1266</v>
       </c>
       <c r="O37" t="s">
-        <v>1453</v>
+        <v>1534</v>
       </c>
       <c r="P37" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B38" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D38" t="s">
         <v>1259</v>
@@ -33264,24 +33264,24 @@
         <v>1354</v>
       </c>
       <c r="K38" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M38" t="s">
         <v>1266</v>
       </c>
       <c r="O38" t="s">
-        <v>1454</v>
+        <v>1535</v>
       </c>
       <c r="P38" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B39" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D39" t="s">
         <v>1259</v>
@@ -33302,24 +33302,24 @@
         <v>1354</v>
       </c>
       <c r="K39" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M39" t="s">
         <v>1266</v>
       </c>
       <c r="O39" t="s">
-        <v>1455</v>
+        <v>1536</v>
       </c>
       <c r="P39" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B40" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D40" t="s">
         <v>1259</v>
@@ -33340,24 +33340,24 @@
         <v>1354</v>
       </c>
       <c r="K40" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M40" t="s">
         <v>1266</v>
       </c>
       <c r="O40" t="s">
-        <v>1456</v>
+        <v>1537</v>
       </c>
       <c r="P40" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B41" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D41" t="s">
         <v>1259</v>
@@ -33378,24 +33378,24 @@
         <v>1354</v>
       </c>
       <c r="K41" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M41" t="s">
         <v>1266</v>
       </c>
       <c r="O41" t="s">
-        <v>1457</v>
+        <v>1538</v>
       </c>
       <c r="P41" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B42" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D42" t="s">
         <v>1259</v>
@@ -33416,24 +33416,24 @@
         <v>1354</v>
       </c>
       <c r="K42" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M42" t="s">
         <v>1266</v>
       </c>
       <c r="O42" t="s">
-        <v>1458</v>
+        <v>1539</v>
       </c>
       <c r="P42" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B43" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D43" t="s">
         <v>1259</v>
@@ -33454,24 +33454,24 @@
         <v>1354</v>
       </c>
       <c r="K43" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M43" t="s">
         <v>1266</v>
       </c>
       <c r="O43" t="s">
-        <v>1459</v>
+        <v>1540</v>
       </c>
       <c r="P43" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B44" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D44" t="s">
         <v>1259</v>
@@ -33492,24 +33492,24 @@
         <v>1354</v>
       </c>
       <c r="K44" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M44" t="s">
         <v>1266</v>
       </c>
       <c r="O44" t="s">
-        <v>1460</v>
+        <v>1541</v>
       </c>
       <c r="P44" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B45" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D45" t="s">
         <v>1259</v>
@@ -33530,24 +33530,24 @@
         <v>1354</v>
       </c>
       <c r="K45" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M45" t="s">
         <v>1266</v>
       </c>
       <c r="O45" t="s">
-        <v>1461</v>
+        <v>1542</v>
       </c>
       <c r="P45" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B46" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D46" t="s">
         <v>1259</v>
@@ -33568,24 +33568,24 @@
         <v>1354</v>
       </c>
       <c r="K46" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M46" t="s">
         <v>1266</v>
       </c>
       <c r="O46" t="s">
-        <v>1462</v>
+        <v>1543</v>
       </c>
       <c r="P46" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B47" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D47" t="s">
         <v>1259</v>
@@ -33606,16 +33606,16 @@
         <v>1354</v>
       </c>
       <c r="K47" t="s">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="M47" t="s">
         <v>1266</v>
       </c>
       <c r="O47" t="s">
-        <v>1463</v>
+        <v>1544</v>
       </c>
       <c r="P47" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
@@ -33681,7 +33681,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B2" t="s">
         <v>1257</v>
@@ -33722,7 +33722,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B3" t="s">
         <v>1269</v>
@@ -33763,7 +33763,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B4" t="s">
         <v>1273</v>
@@ -33804,7 +33804,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B5" t="s">
         <v>1277</v>
@@ -33845,7 +33845,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B6" t="s">
         <v>1281</v>
@@ -33886,7 +33886,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B7" t="s">
         <v>1285</v>
@@ -33927,7 +33927,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B8" t="s">
         <v>1289</v>
@@ -33971,7 +33971,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B9" t="s">
         <v>1298</v>
@@ -34015,7 +34015,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B10" t="s">
         <v>1303</v>
@@ -34059,7 +34059,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B11" t="s">
         <v>1308</v>
@@ -34103,7 +34103,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B12" t="s">
         <v>1313</v>
@@ -34144,7 +34144,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B13" t="s">
         <v>1317</v>
@@ -34191,7 +34191,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B14" t="s">
         <v>1325</v>
@@ -34235,7 +34235,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B15" t="s">
         <v>1331</v>
@@ -34279,7 +34279,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B16" t="s">
         <v>1338</v>
@@ -34323,7 +34323,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B17" t="s">
         <v>1344</v>
@@ -34364,7 +34364,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B18" t="s">
         <v>1349</v>
@@ -34388,13 +34388,13 @@
         <v>1354</v>
       </c>
       <c r="K18" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M18" t="s">
         <v>1266</v>
       </c>
       <c r="O18" t="s">
-        <v>1465</v>
+        <v>1417</v>
       </c>
       <c r="P18" t="s">
         <v>1356</v>
@@ -34402,7 +34402,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B19" t="s">
         <v>1349</v>
@@ -34426,13 +34426,13 @@
         <v>1354</v>
       </c>
       <c r="K19" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M19" t="s">
         <v>1266</v>
       </c>
       <c r="O19" t="s">
-        <v>1466</v>
+        <v>1418</v>
       </c>
       <c r="P19" t="s">
         <v>1358</v>
@@ -34440,7 +34440,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B20" t="s">
         <v>1349</v>
@@ -34464,13 +34464,13 @@
         <v>1354</v>
       </c>
       <c r="K20" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M20" t="s">
         <v>1266</v>
       </c>
       <c r="O20" t="s">
-        <v>1467</v>
+        <v>1419</v>
       </c>
       <c r="P20" t="s">
         <v>1360</v>
@@ -34478,7 +34478,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B21" t="s">
         <v>1349</v>
@@ -34502,13 +34502,13 @@
         <v>1354</v>
       </c>
       <c r="K21" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M21" t="s">
         <v>1266</v>
       </c>
       <c r="O21" t="s">
-        <v>1468</v>
+        <v>1420</v>
       </c>
       <c r="P21" t="s">
         <v>1362</v>
@@ -34516,7 +34516,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B22" t="s">
         <v>1349</v>
@@ -34540,13 +34540,13 @@
         <v>1354</v>
       </c>
       <c r="K22" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M22" t="s">
         <v>1266</v>
       </c>
       <c r="O22" t="s">
-        <v>1469</v>
+        <v>1421</v>
       </c>
       <c r="P22" t="s">
         <v>1364</v>
@@ -34554,7 +34554,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B23" t="s">
         <v>1365</v>
@@ -34578,13 +34578,13 @@
         <v>1354</v>
       </c>
       <c r="K23" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M23" t="s">
         <v>1266</v>
       </c>
       <c r="O23" t="s">
-        <v>1470</v>
+        <v>1422</v>
       </c>
       <c r="P23" t="s">
         <v>1356</v>
@@ -34592,7 +34592,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B24" t="s">
         <v>1365</v>
@@ -34616,13 +34616,13 @@
         <v>1354</v>
       </c>
       <c r="K24" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M24" t="s">
         <v>1266</v>
       </c>
       <c r="O24" t="s">
-        <v>1471</v>
+        <v>1423</v>
       </c>
       <c r="P24" t="s">
         <v>1358</v>
@@ -34630,7 +34630,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B25" t="s">
         <v>1365</v>
@@ -34654,13 +34654,13 @@
         <v>1354</v>
       </c>
       <c r="K25" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M25" t="s">
         <v>1266</v>
       </c>
       <c r="O25" t="s">
-        <v>1472</v>
+        <v>1424</v>
       </c>
       <c r="P25" t="s">
         <v>1360</v>
@@ -34668,7 +34668,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B26" t="s">
         <v>1365</v>
@@ -34692,13 +34692,13 @@
         <v>1354</v>
       </c>
       <c r="K26" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M26" t="s">
         <v>1266</v>
       </c>
       <c r="O26" t="s">
-        <v>1473</v>
+        <v>1425</v>
       </c>
       <c r="P26" t="s">
         <v>1362</v>
@@ -34706,7 +34706,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B27" t="s">
         <v>1365</v>
@@ -34730,13 +34730,13 @@
         <v>1354</v>
       </c>
       <c r="K27" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M27" t="s">
         <v>1266</v>
       </c>
       <c r="O27" t="s">
-        <v>1474</v>
+        <v>1426</v>
       </c>
       <c r="P27" t="s">
         <v>1364</v>
@@ -34744,7 +34744,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B28" t="s">
         <v>1371</v>
@@ -34768,13 +34768,13 @@
         <v>1354</v>
       </c>
       <c r="K28" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M28" t="s">
         <v>1266</v>
       </c>
       <c r="O28" t="s">
-        <v>1475</v>
+        <v>1427</v>
       </c>
       <c r="P28" t="s">
         <v>1356</v>
@@ -34782,7 +34782,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B29" t="s">
         <v>1371</v>
@@ -34806,13 +34806,13 @@
         <v>1354</v>
       </c>
       <c r="K29" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M29" t="s">
         <v>1266</v>
       </c>
       <c r="O29" t="s">
-        <v>1476</v>
+        <v>1428</v>
       </c>
       <c r="P29" t="s">
         <v>1358</v>
@@ -34820,7 +34820,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B30" t="s">
         <v>1371</v>
@@ -34844,13 +34844,13 @@
         <v>1354</v>
       </c>
       <c r="K30" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M30" t="s">
         <v>1266</v>
       </c>
       <c r="O30" t="s">
-        <v>1477</v>
+        <v>1429</v>
       </c>
       <c r="P30" t="s">
         <v>1360</v>
@@ -34858,7 +34858,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B31" t="s">
         <v>1371</v>
@@ -34882,13 +34882,13 @@
         <v>1354</v>
       </c>
       <c r="K31" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M31" t="s">
         <v>1266</v>
       </c>
       <c r="O31" t="s">
-        <v>1478</v>
+        <v>1430</v>
       </c>
       <c r="P31" t="s">
         <v>1362</v>
@@ -34896,7 +34896,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B32" t="s">
         <v>1371</v>
@@ -34920,13 +34920,13 @@
         <v>1354</v>
       </c>
       <c r="K32" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M32" t="s">
         <v>1266</v>
       </c>
       <c r="O32" t="s">
-        <v>1479</v>
+        <v>1431</v>
       </c>
       <c r="P32" t="s">
         <v>1364</v>
@@ -34934,7 +34934,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B33" t="s">
         <v>1377</v>
@@ -34958,21 +34958,21 @@
         <v>1354</v>
       </c>
       <c r="K33" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M33" t="s">
         <v>1266</v>
       </c>
       <c r="O33" t="s">
-        <v>1480</v>
+        <v>1545</v>
       </c>
       <c r="P33" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B34" t="s">
         <v>1377</v>
@@ -34996,21 +34996,21 @@
         <v>1354</v>
       </c>
       <c r="K34" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M34" t="s">
         <v>1266</v>
       </c>
       <c r="O34" t="s">
-        <v>1481</v>
+        <v>1546</v>
       </c>
       <c r="P34" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B35" t="s">
         <v>1377</v>
@@ -35034,24 +35034,24 @@
         <v>1354</v>
       </c>
       <c r="K35" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M35" t="s">
         <v>1266</v>
       </c>
       <c r="O35" t="s">
-        <v>1482</v>
+        <v>1547</v>
       </c>
       <c r="P35" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B36" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D36" t="s">
         <v>1259</v>
@@ -35072,24 +35072,24 @@
         <v>1354</v>
       </c>
       <c r="K36" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M36" t="s">
         <v>1266</v>
       </c>
       <c r="O36" t="s">
-        <v>1483</v>
+        <v>1548</v>
       </c>
       <c r="P36" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B37" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="s">
         <v>1259</v>
@@ -35110,24 +35110,24 @@
         <v>1354</v>
       </c>
       <c r="K37" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M37" t="s">
         <v>1266</v>
       </c>
       <c r="O37" t="s">
-        <v>1484</v>
+        <v>1549</v>
       </c>
       <c r="P37" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B38" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D38" t="s">
         <v>1259</v>
@@ -35148,24 +35148,24 @@
         <v>1354</v>
       </c>
       <c r="K38" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M38" t="s">
         <v>1266</v>
       </c>
       <c r="O38" t="s">
-        <v>1485</v>
+        <v>1550</v>
       </c>
       <c r="P38" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B39" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D39" t="s">
         <v>1259</v>
@@ -35186,24 +35186,24 @@
         <v>1354</v>
       </c>
       <c r="K39" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M39" t="s">
         <v>1266</v>
       </c>
       <c r="O39" t="s">
-        <v>1486</v>
+        <v>1551</v>
       </c>
       <c r="P39" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B40" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D40" t="s">
         <v>1259</v>
@@ -35224,24 +35224,24 @@
         <v>1354</v>
       </c>
       <c r="K40" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M40" t="s">
         <v>1266</v>
       </c>
       <c r="O40" t="s">
-        <v>1487</v>
+        <v>1552</v>
       </c>
       <c r="P40" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B41" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D41" t="s">
         <v>1259</v>
@@ -35262,24 +35262,24 @@
         <v>1354</v>
       </c>
       <c r="K41" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M41" t="s">
         <v>1266</v>
       </c>
       <c r="O41" t="s">
-        <v>1488</v>
+        <v>1553</v>
       </c>
       <c r="P41" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B42" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D42" t="s">
         <v>1259</v>
@@ -35300,24 +35300,24 @@
         <v>1354</v>
       </c>
       <c r="K42" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M42" t="s">
         <v>1266</v>
       </c>
       <c r="O42" t="s">
-        <v>1489</v>
+        <v>1554</v>
       </c>
       <c r="P42" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B43" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D43" t="s">
         <v>1259</v>
@@ -35338,24 +35338,24 @@
         <v>1354</v>
       </c>
       <c r="K43" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M43" t="s">
         <v>1266</v>
       </c>
       <c r="O43" t="s">
-        <v>1490</v>
+        <v>1555</v>
       </c>
       <c r="P43" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B44" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D44" t="s">
         <v>1259</v>
@@ -35376,24 +35376,24 @@
         <v>1354</v>
       </c>
       <c r="K44" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M44" t="s">
         <v>1266</v>
       </c>
       <c r="O44" t="s">
-        <v>1491</v>
+        <v>1556</v>
       </c>
       <c r="P44" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B45" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D45" t="s">
         <v>1259</v>
@@ -35414,24 +35414,24 @@
         <v>1354</v>
       </c>
       <c r="K45" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M45" t="s">
         <v>1266</v>
       </c>
       <c r="O45" t="s">
-        <v>1492</v>
+        <v>1557</v>
       </c>
       <c r="P45" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B46" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D46" t="s">
         <v>1259</v>
@@ -35452,24 +35452,24 @@
         <v>1354</v>
       </c>
       <c r="K46" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M46" t="s">
         <v>1266</v>
       </c>
       <c r="O46" t="s">
-        <v>1493</v>
+        <v>1558</v>
       </c>
       <c r="P46" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="B47" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D47" t="s">
         <v>1259</v>
@@ -35490,16 +35490,16 @@
         <v>1354</v>
       </c>
       <c r="K47" t="s">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="M47" t="s">
         <v>1266</v>
       </c>
       <c r="O47" t="s">
-        <v>1494</v>
+        <v>1559</v>
       </c>
       <c r="P47" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
@@ -35565,7 +35565,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B2" t="s">
         <v>1257</v>
@@ -35606,7 +35606,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B3" t="s">
         <v>1269</v>
@@ -35647,7 +35647,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B4" t="s">
         <v>1273</v>
@@ -35688,7 +35688,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B5" t="s">
         <v>1277</v>
@@ -35729,7 +35729,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B6" t="s">
         <v>1281</v>
@@ -35770,7 +35770,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B7" t="s">
         <v>1285</v>
@@ -35811,7 +35811,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B8" t="s">
         <v>1289</v>
@@ -35855,7 +35855,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B9" t="s">
         <v>1298</v>
@@ -35899,7 +35899,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B10" t="s">
         <v>1303</v>
@@ -35943,7 +35943,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B11" t="s">
         <v>1308</v>
@@ -35987,7 +35987,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B12" t="s">
         <v>1313</v>
@@ -36028,7 +36028,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B13" t="s">
         <v>1317</v>
@@ -36075,7 +36075,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B14" t="s">
         <v>1325</v>
@@ -36119,7 +36119,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B15" t="s">
         <v>1331</v>
@@ -36163,7 +36163,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B16" t="s">
         <v>1338</v>
@@ -36207,7 +36207,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B17" t="s">
         <v>1344</v>
@@ -36248,7 +36248,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B18" t="s">
         <v>1349</v>
@@ -36272,13 +36272,13 @@
         <v>1354</v>
       </c>
       <c r="K18" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M18" t="s">
         <v>1266</v>
       </c>
       <c r="O18" t="s">
-        <v>1496</v>
+        <v>1433</v>
       </c>
       <c r="P18" t="s">
         <v>1356</v>
@@ -36286,7 +36286,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B19" t="s">
         <v>1349</v>
@@ -36310,13 +36310,13 @@
         <v>1354</v>
       </c>
       <c r="K19" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M19" t="s">
         <v>1266</v>
       </c>
       <c r="O19" t="s">
-        <v>1497</v>
+        <v>1434</v>
       </c>
       <c r="P19" t="s">
         <v>1358</v>
@@ -36324,7 +36324,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B20" t="s">
         <v>1349</v>
@@ -36348,13 +36348,13 @@
         <v>1354</v>
       </c>
       <c r="K20" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M20" t="s">
         <v>1266</v>
       </c>
       <c r="O20" t="s">
-        <v>1498</v>
+        <v>1435</v>
       </c>
       <c r="P20" t="s">
         <v>1360</v>
@@ -36362,7 +36362,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B21" t="s">
         <v>1349</v>
@@ -36386,13 +36386,13 @@
         <v>1354</v>
       </c>
       <c r="K21" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M21" t="s">
         <v>1266</v>
       </c>
       <c r="O21" t="s">
-        <v>1499</v>
+        <v>1436</v>
       </c>
       <c r="P21" t="s">
         <v>1362</v>
@@ -36400,7 +36400,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B22" t="s">
         <v>1349</v>
@@ -36424,13 +36424,13 @@
         <v>1354</v>
       </c>
       <c r="K22" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M22" t="s">
         <v>1266</v>
       </c>
       <c r="O22" t="s">
-        <v>1500</v>
+        <v>1437</v>
       </c>
       <c r="P22" t="s">
         <v>1364</v>
@@ -36438,7 +36438,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B23" t="s">
         <v>1365</v>
@@ -36462,13 +36462,13 @@
         <v>1354</v>
       </c>
       <c r="K23" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M23" t="s">
         <v>1266</v>
       </c>
       <c r="O23" t="s">
-        <v>1501</v>
+        <v>1438</v>
       </c>
       <c r="P23" t="s">
         <v>1356</v>
@@ -36476,7 +36476,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B24" t="s">
         <v>1365</v>
@@ -36500,13 +36500,13 @@
         <v>1354</v>
       </c>
       <c r="K24" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M24" t="s">
         <v>1266</v>
       </c>
       <c r="O24" t="s">
-        <v>1502</v>
+        <v>1439</v>
       </c>
       <c r="P24" t="s">
         <v>1358</v>
@@ -36514,7 +36514,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B25" t="s">
         <v>1365</v>
@@ -36538,13 +36538,13 @@
         <v>1354</v>
       </c>
       <c r="K25" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M25" t="s">
         <v>1266</v>
       </c>
       <c r="O25" t="s">
-        <v>1503</v>
+        <v>1440</v>
       </c>
       <c r="P25" t="s">
         <v>1360</v>
@@ -36552,7 +36552,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B26" t="s">
         <v>1365</v>
@@ -36576,13 +36576,13 @@
         <v>1354</v>
       </c>
       <c r="K26" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M26" t="s">
         <v>1266</v>
       </c>
       <c r="O26" t="s">
-        <v>1504</v>
+        <v>1441</v>
       </c>
       <c r="P26" t="s">
         <v>1362</v>
@@ -36590,7 +36590,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B27" t="s">
         <v>1365</v>
@@ -36614,13 +36614,13 @@
         <v>1354</v>
       </c>
       <c r="K27" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M27" t="s">
         <v>1266</v>
       </c>
       <c r="O27" t="s">
-        <v>1505</v>
+        <v>1442</v>
       </c>
       <c r="P27" t="s">
         <v>1364</v>
@@ -36628,7 +36628,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B28" t="s">
         <v>1371</v>
@@ -36652,13 +36652,13 @@
         <v>1354</v>
       </c>
       <c r="K28" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M28" t="s">
         <v>1266</v>
       </c>
       <c r="O28" t="s">
-        <v>1506</v>
+        <v>1443</v>
       </c>
       <c r="P28" t="s">
         <v>1356</v>
@@ -36666,7 +36666,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B29" t="s">
         <v>1371</v>
@@ -36690,13 +36690,13 @@
         <v>1354</v>
       </c>
       <c r="K29" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M29" t="s">
         <v>1266</v>
       </c>
       <c r="O29" t="s">
-        <v>1507</v>
+        <v>1444</v>
       </c>
       <c r="P29" t="s">
         <v>1358</v>
@@ -36704,7 +36704,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B30" t="s">
         <v>1371</v>
@@ -36728,13 +36728,13 @@
         <v>1354</v>
       </c>
       <c r="K30" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M30" t="s">
         <v>1266</v>
       </c>
       <c r="O30" t="s">
-        <v>1508</v>
+        <v>1445</v>
       </c>
       <c r="P30" t="s">
         <v>1360</v>
@@ -36742,7 +36742,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B31" t="s">
         <v>1371</v>
@@ -36766,13 +36766,13 @@
         <v>1354</v>
       </c>
       <c r="K31" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M31" t="s">
         <v>1266</v>
       </c>
       <c r="O31" t="s">
-        <v>1509</v>
+        <v>1446</v>
       </c>
       <c r="P31" t="s">
         <v>1362</v>
@@ -36780,7 +36780,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B32" t="s">
         <v>1371</v>
@@ -36804,13 +36804,13 @@
         <v>1354</v>
       </c>
       <c r="K32" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M32" t="s">
         <v>1266</v>
       </c>
       <c r="O32" t="s">
-        <v>1510</v>
+        <v>1447</v>
       </c>
       <c r="P32" t="s">
         <v>1364</v>
@@ -36818,7 +36818,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B33" t="s">
         <v>1377</v>
@@ -36842,21 +36842,21 @@
         <v>1354</v>
       </c>
       <c r="K33" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M33" t="s">
         <v>1266</v>
       </c>
       <c r="O33" t="s">
-        <v>1511</v>
+        <v>1560</v>
       </c>
       <c r="P33" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B34" t="s">
         <v>1377</v>
@@ -36880,21 +36880,21 @@
         <v>1354</v>
       </c>
       <c r="K34" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M34" t="s">
         <v>1266</v>
       </c>
       <c r="O34" t="s">
-        <v>1512</v>
+        <v>1561</v>
       </c>
       <c r="P34" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B35" t="s">
         <v>1377</v>
@@ -36918,24 +36918,24 @@
         <v>1354</v>
       </c>
       <c r="K35" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M35" t="s">
         <v>1266</v>
       </c>
       <c r="O35" t="s">
-        <v>1513</v>
+        <v>1562</v>
       </c>
       <c r="P35" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B36" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D36" t="s">
         <v>1259</v>
@@ -36956,24 +36956,24 @@
         <v>1354</v>
       </c>
       <c r="K36" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M36" t="s">
         <v>1266</v>
       </c>
       <c r="O36" t="s">
-        <v>1514</v>
+        <v>1563</v>
       </c>
       <c r="P36" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B37" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="s">
         <v>1259</v>
@@ -36994,24 +36994,24 @@
         <v>1354</v>
       </c>
       <c r="K37" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M37" t="s">
         <v>1266</v>
       </c>
       <c r="O37" t="s">
-        <v>1515</v>
+        <v>1564</v>
       </c>
       <c r="P37" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B38" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D38" t="s">
         <v>1259</v>
@@ -37032,24 +37032,24 @@
         <v>1354</v>
       </c>
       <c r="K38" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M38" t="s">
         <v>1266</v>
       </c>
       <c r="O38" t="s">
-        <v>1516</v>
+        <v>1565</v>
       </c>
       <c r="P38" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B39" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D39" t="s">
         <v>1259</v>
@@ -37070,24 +37070,24 @@
         <v>1354</v>
       </c>
       <c r="K39" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M39" t="s">
         <v>1266</v>
       </c>
       <c r="O39" t="s">
-        <v>1517</v>
+        <v>1566</v>
       </c>
       <c r="P39" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B40" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D40" t="s">
         <v>1259</v>
@@ -37108,24 +37108,24 @@
         <v>1354</v>
       </c>
       <c r="K40" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M40" t="s">
         <v>1266</v>
       </c>
       <c r="O40" t="s">
-        <v>1518</v>
+        <v>1567</v>
       </c>
       <c r="P40" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B41" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D41" t="s">
         <v>1259</v>
@@ -37146,24 +37146,24 @@
         <v>1354</v>
       </c>
       <c r="K41" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M41" t="s">
         <v>1266</v>
       </c>
       <c r="O41" t="s">
-        <v>1519</v>
+        <v>1568</v>
       </c>
       <c r="P41" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B42" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D42" t="s">
         <v>1259</v>
@@ -37184,24 +37184,24 @@
         <v>1354</v>
       </c>
       <c r="K42" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M42" t="s">
         <v>1266</v>
       </c>
       <c r="O42" t="s">
-        <v>1520</v>
+        <v>1569</v>
       </c>
       <c r="P42" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B43" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D43" t="s">
         <v>1259</v>
@@ -37222,24 +37222,24 @@
         <v>1354</v>
       </c>
       <c r="K43" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M43" t="s">
         <v>1266</v>
       </c>
       <c r="O43" t="s">
-        <v>1521</v>
+        <v>1570</v>
       </c>
       <c r="P43" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B44" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D44" t="s">
         <v>1259</v>
@@ -37260,24 +37260,24 @@
         <v>1354</v>
       </c>
       <c r="K44" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M44" t="s">
         <v>1266</v>
       </c>
       <c r="O44" t="s">
-        <v>1522</v>
+        <v>1571</v>
       </c>
       <c r="P44" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B45" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D45" t="s">
         <v>1259</v>
@@ -37298,24 +37298,24 @@
         <v>1354</v>
       </c>
       <c r="K45" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M45" t="s">
         <v>1266</v>
       </c>
       <c r="O45" t="s">
-        <v>1523</v>
+        <v>1572</v>
       </c>
       <c r="P45" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B46" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D46" t="s">
         <v>1259</v>
@@ -37336,24 +37336,24 @@
         <v>1354</v>
       </c>
       <c r="K46" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M46" t="s">
         <v>1266</v>
       </c>
       <c r="O46" t="s">
-        <v>1524</v>
+        <v>1573</v>
       </c>
       <c r="P46" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="B47" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D47" t="s">
         <v>1259</v>
@@ -37374,16 +37374,16 @@
         <v>1354</v>
       </c>
       <c r="K47" t="s">
-        <v>1495</v>
+        <v>1432</v>
       </c>
       <c r="M47" t="s">
         <v>1266</v>
       </c>
       <c r="O47" t="s">
-        <v>1525</v>
+        <v>1574</v>
       </c>
       <c r="P47" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
@@ -37449,7 +37449,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B2" t="s">
         <v>1257</v>
@@ -37490,7 +37490,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B3" t="s">
         <v>1269</v>
@@ -37531,7 +37531,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B4" t="s">
         <v>1273</v>
@@ -37572,7 +37572,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B5" t="s">
         <v>1277</v>
@@ -37613,7 +37613,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B6" t="s">
         <v>1281</v>
@@ -37654,7 +37654,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B7" t="s">
         <v>1285</v>
@@ -37695,7 +37695,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B8" t="s">
         <v>1289</v>
@@ -37739,7 +37739,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B9" t="s">
         <v>1298</v>
@@ -37783,7 +37783,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B10" t="s">
         <v>1303</v>
@@ -37827,7 +37827,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B11" t="s">
         <v>1308</v>
@@ -37871,7 +37871,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B12" t="s">
         <v>1313</v>
@@ -37912,7 +37912,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B13" t="s">
         <v>1317</v>
@@ -37959,7 +37959,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B14" t="s">
         <v>1325</v>
@@ -38003,7 +38003,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B15" t="s">
         <v>1331</v>
@@ -38047,7 +38047,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B16" t="s">
         <v>1338</v>
@@ -38091,7 +38091,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B17" t="s">
         <v>1344</v>
@@ -38132,7 +38132,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B18" t="s">
         <v>1349</v>
@@ -38156,13 +38156,13 @@
         <v>1354</v>
       </c>
       <c r="K18" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M18" t="s">
         <v>1266</v>
       </c>
       <c r="O18" t="s">
-        <v>1527</v>
+        <v>1449</v>
       </c>
       <c r="P18" t="s">
         <v>1356</v>
@@ -38170,7 +38170,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B19" t="s">
         <v>1349</v>
@@ -38194,13 +38194,13 @@
         <v>1354</v>
       </c>
       <c r="K19" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M19" t="s">
         <v>1266</v>
       </c>
       <c r="O19" t="s">
-        <v>1528</v>
+        <v>1450</v>
       </c>
       <c r="P19" t="s">
         <v>1358</v>
@@ -38208,7 +38208,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B20" t="s">
         <v>1349</v>
@@ -38232,13 +38232,13 @@
         <v>1354</v>
       </c>
       <c r="K20" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M20" t="s">
         <v>1266</v>
       </c>
       <c r="O20" t="s">
-        <v>1529</v>
+        <v>1451</v>
       </c>
       <c r="P20" t="s">
         <v>1360</v>
@@ -38246,7 +38246,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B21" t="s">
         <v>1349</v>
@@ -38270,13 +38270,13 @@
         <v>1354</v>
       </c>
       <c r="K21" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M21" t="s">
         <v>1266</v>
       </c>
       <c r="O21" t="s">
-        <v>1530</v>
+        <v>1452</v>
       </c>
       <c r="P21" t="s">
         <v>1362</v>
@@ -38284,7 +38284,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B22" t="s">
         <v>1349</v>
@@ -38308,13 +38308,13 @@
         <v>1354</v>
       </c>
       <c r="K22" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M22" t="s">
         <v>1266</v>
       </c>
       <c r="O22" t="s">
-        <v>1531</v>
+        <v>1453</v>
       </c>
       <c r="P22" t="s">
         <v>1364</v>
@@ -38322,7 +38322,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B23" t="s">
         <v>1365</v>
@@ -38346,13 +38346,13 @@
         <v>1354</v>
       </c>
       <c r="K23" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M23" t="s">
         <v>1266</v>
       </c>
       <c r="O23" t="s">
-        <v>1532</v>
+        <v>1454</v>
       </c>
       <c r="P23" t="s">
         <v>1356</v>
@@ -38360,7 +38360,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B24" t="s">
         <v>1365</v>
@@ -38384,13 +38384,13 @@
         <v>1354</v>
       </c>
       <c r="K24" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M24" t="s">
         <v>1266</v>
       </c>
       <c r="O24" t="s">
-        <v>1533</v>
+        <v>1455</v>
       </c>
       <c r="P24" t="s">
         <v>1358</v>
@@ -38398,7 +38398,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B25" t="s">
         <v>1365</v>
@@ -38422,13 +38422,13 @@
         <v>1354</v>
       </c>
       <c r="K25" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M25" t="s">
         <v>1266</v>
       </c>
       <c r="O25" t="s">
-        <v>1534</v>
+        <v>1456</v>
       </c>
       <c r="P25" t="s">
         <v>1360</v>
@@ -38436,7 +38436,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B26" t="s">
         <v>1365</v>
@@ -38460,13 +38460,13 @@
         <v>1354</v>
       </c>
       <c r="K26" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M26" t="s">
         <v>1266</v>
       </c>
       <c r="O26" t="s">
-        <v>1535</v>
+        <v>1457</v>
       </c>
       <c r="P26" t="s">
         <v>1362</v>
@@ -38474,7 +38474,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B27" t="s">
         <v>1365</v>
@@ -38498,13 +38498,13 @@
         <v>1354</v>
       </c>
       <c r="K27" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M27" t="s">
         <v>1266</v>
       </c>
       <c r="O27" t="s">
-        <v>1536</v>
+        <v>1458</v>
       </c>
       <c r="P27" t="s">
         <v>1364</v>
@@ -38512,7 +38512,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B28" t="s">
         <v>1371</v>
@@ -38536,13 +38536,13 @@
         <v>1354</v>
       </c>
       <c r="K28" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M28" t="s">
         <v>1266</v>
       </c>
       <c r="O28" t="s">
-        <v>1537</v>
+        <v>1459</v>
       </c>
       <c r="P28" t="s">
         <v>1356</v>
@@ -38550,7 +38550,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B29" t="s">
         <v>1371</v>
@@ -38574,13 +38574,13 @@
         <v>1354</v>
       </c>
       <c r="K29" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M29" t="s">
         <v>1266</v>
       </c>
       <c r="O29" t="s">
-        <v>1538</v>
+        <v>1460</v>
       </c>
       <c r="P29" t="s">
         <v>1358</v>
@@ -38588,7 +38588,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B30" t="s">
         <v>1371</v>
@@ -38612,13 +38612,13 @@
         <v>1354</v>
       </c>
       <c r="K30" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M30" t="s">
         <v>1266</v>
       </c>
       <c r="O30" t="s">
-        <v>1539</v>
+        <v>1461</v>
       </c>
       <c r="P30" t="s">
         <v>1360</v>
@@ -38626,7 +38626,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B31" t="s">
         <v>1371</v>
@@ -38650,13 +38650,13 @@
         <v>1354</v>
       </c>
       <c r="K31" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M31" t="s">
         <v>1266</v>
       </c>
       <c r="O31" t="s">
-        <v>1540</v>
+        <v>1462</v>
       </c>
       <c r="P31" t="s">
         <v>1362</v>
@@ -38664,7 +38664,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B32" t="s">
         <v>1371</v>
@@ -38688,13 +38688,13 @@
         <v>1354</v>
       </c>
       <c r="K32" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M32" t="s">
         <v>1266</v>
       </c>
       <c r="O32" t="s">
-        <v>1541</v>
+        <v>1463</v>
       </c>
       <c r="P32" t="s">
         <v>1364</v>
@@ -38702,7 +38702,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B33" t="s">
         <v>1377</v>
@@ -38726,21 +38726,21 @@
         <v>1354</v>
       </c>
       <c r="K33" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M33" t="s">
         <v>1266</v>
       </c>
       <c r="O33" t="s">
-        <v>1542</v>
+        <v>1575</v>
       </c>
       <c r="P33" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B34" t="s">
         <v>1377</v>
@@ -38764,21 +38764,21 @@
         <v>1354</v>
       </c>
       <c r="K34" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M34" t="s">
         <v>1266</v>
       </c>
       <c r="O34" t="s">
-        <v>1543</v>
+        <v>1576</v>
       </c>
       <c r="P34" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B35" t="s">
         <v>1377</v>
@@ -38802,24 +38802,24 @@
         <v>1354</v>
       </c>
       <c r="K35" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M35" t="s">
         <v>1266</v>
       </c>
       <c r="O35" t="s">
-        <v>1544</v>
+        <v>1577</v>
       </c>
       <c r="P35" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B36" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D36" t="s">
         <v>1259</v>
@@ -38840,24 +38840,24 @@
         <v>1354</v>
       </c>
       <c r="K36" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M36" t="s">
         <v>1266</v>
       </c>
       <c r="O36" t="s">
-        <v>1545</v>
+        <v>1578</v>
       </c>
       <c r="P36" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B37" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="s">
         <v>1259</v>
@@ -38878,24 +38878,24 @@
         <v>1354</v>
       </c>
       <c r="K37" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M37" t="s">
         <v>1266</v>
       </c>
       <c r="O37" t="s">
-        <v>1546</v>
+        <v>1579</v>
       </c>
       <c r="P37" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B38" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="D38" t="s">
         <v>1259</v>
@@ -38916,24 +38916,24 @@
         <v>1354</v>
       </c>
       <c r="K38" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M38" t="s">
         <v>1266</v>
       </c>
       <c r="O38" t="s">
-        <v>1547</v>
+        <v>1580</v>
       </c>
       <c r="P38" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B39" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D39" t="s">
         <v>1259</v>
@@ -38954,24 +38954,24 @@
         <v>1354</v>
       </c>
       <c r="K39" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M39" t="s">
         <v>1266</v>
       </c>
       <c r="O39" t="s">
-        <v>1548</v>
+        <v>1581</v>
       </c>
       <c r="P39" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B40" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D40" t="s">
         <v>1259</v>
@@ -38992,24 +38992,24 @@
         <v>1354</v>
       </c>
       <c r="K40" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M40" t="s">
         <v>1266</v>
       </c>
       <c r="O40" t="s">
-        <v>1549</v>
+        <v>1582</v>
       </c>
       <c r="P40" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B41" t="s">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="D41" t="s">
         <v>1259</v>
@@ -39030,24 +39030,24 @@
         <v>1354</v>
       </c>
       <c r="K41" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M41" t="s">
         <v>1266</v>
       </c>
       <c r="O41" t="s">
-        <v>1550</v>
+        <v>1583</v>
       </c>
       <c r="P41" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B42" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D42" t="s">
         <v>1259</v>
@@ -39068,24 +39068,24 @@
         <v>1354</v>
       </c>
       <c r="K42" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M42" t="s">
         <v>1266</v>
       </c>
       <c r="O42" t="s">
-        <v>1551</v>
+        <v>1584</v>
       </c>
       <c r="P42" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B43" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D43" t="s">
         <v>1259</v>
@@ -39106,24 +39106,24 @@
         <v>1354</v>
       </c>
       <c r="K43" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M43" t="s">
         <v>1266</v>
       </c>
       <c r="O43" t="s">
-        <v>1552</v>
+        <v>1585</v>
       </c>
       <c r="P43" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B44" t="s">
-        <v>1394</v>
+        <v>1382</v>
       </c>
       <c r="D44" t="s">
         <v>1259</v>
@@ -39144,24 +39144,24 @@
         <v>1354</v>
       </c>
       <c r="K44" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M44" t="s">
         <v>1266</v>
       </c>
       <c r="O44" t="s">
-        <v>1553</v>
+        <v>1586</v>
       </c>
       <c r="P44" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B45" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D45" t="s">
         <v>1259</v>
@@ -39182,24 +39182,24 @@
         <v>1354</v>
       </c>
       <c r="K45" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M45" t="s">
         <v>1266</v>
       </c>
       <c r="O45" t="s">
-        <v>1554</v>
+        <v>1587</v>
       </c>
       <c r="P45" t="s">
-        <v>1381</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B46" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D46" t="s">
         <v>1259</v>
@@ -39220,24 +39220,24 @@
         <v>1354</v>
       </c>
       <c r="K46" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M46" t="s">
         <v>1266</v>
       </c>
       <c r="O46" t="s">
-        <v>1555</v>
+        <v>1588</v>
       </c>
       <c r="P46" t="s">
-        <v>1383</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="B47" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D47" t="s">
         <v>1259</v>
@@ -39258,16 +39258,16 @@
         <v>1354</v>
       </c>
       <c r="K47" t="s">
-        <v>1526</v>
+        <v>1448</v>
       </c>
       <c r="M47" t="s">
         <v>1266</v>
       </c>
       <c r="O47" t="s">
-        <v>1556</v>
+        <v>1589</v>
       </c>
       <c r="P47" t="s">
-        <v>1385</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
